--- a/CCU/EtOH/analyses/parameter_distributions/parameter-distributions_full.xlsx
+++ b/CCU/EtOH/analyses/parameter_distributions/parameter-distributions_full.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IGB\Documents\GitHub\CCU\CCU\EtOH\analyses\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA2F9B1-ABB9-4A13-9A16-8D36FC5B1562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0188EC33-454E-4ADA-8B8D-793841E2C17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,7 +556,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -574,6 +574,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -635,10 +643,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -656,8 +665,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2185,7 +2196,7 @@
         <v>12</v>
       </c>
       <c r="G38" s="3">
-        <f t="shared" ref="G38:G52" si="3">E38*0.8</f>
+        <f t="shared" ref="G38:G51" si="3">E38*0.8</f>
         <v>1.1519999999999999</v>
       </c>
       <c r="I38" s="3">
@@ -2529,11 +2540,11 @@
         <v>8</v>
       </c>
       <c r="H48" s="3">
-        <f t="shared" ref="H48:H52" si="7">E48</f>
+        <f t="shared" ref="H48:H51" si="7">E48</f>
         <v>10</v>
       </c>
       <c r="I48" s="3">
-        <f t="shared" ref="I48:I52" si="8">E48*1.2</f>
+        <f t="shared" ref="I48:I51" si="8">E48*1.2</f>
         <v>12</v>
       </c>
       <c r="J48" s="3" t="s">
@@ -2659,23 +2670,20 @@
         <v>64</v>
       </c>
       <c r="E52" s="3">
-        <f>1208000/500000*24</f>
-        <v>57.983999999999995</v>
+        <f>H52</f>
+        <v>52.4</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>18</v>
       </c>
       <c r="G52" s="3">
-        <f t="shared" si="3"/>
-        <v>46.3872</v>
+        <v>48</v>
       </c>
       <c r="H52" s="3">
-        <f t="shared" si="7"/>
-        <v>57.983999999999995</v>
+        <v>52.4</v>
       </c>
       <c r="I52" s="3">
-        <f t="shared" si="8"/>
-        <v>69.580799999999996</v>
+        <v>52.8</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>109</v>
@@ -2890,7 +2898,7 @@
       <c r="J58" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K58" t="s">
+      <c r="K58" s="9" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3121,8 +3129,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="K58" r:id="rId1" xr:uid="{DD55F3D7-C741-4FAC-A1CE-89A46E4BB25C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/CCU/EtOH/analyses/parameter_distributions/parameter-distributions_full.xlsx
+++ b/CCU/EtOH/analyses/parameter_distributions/parameter-distributions_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IGB\Documents\GitHub\CCU\CCU\EtOH\analyses\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0188EC33-454E-4ADA-8B8D-793841E2C17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE27D1B4-56F3-4985-AD16-B9D3C1DED7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1441,7 +1441,7 @@
         <v>0.11895995005808951</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1472,7 +1472,7 @@
         <v>1.4411192147993641</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">

--- a/CCU/EtOH/analyses/parameter_distributions/parameter-distributions_full.xlsx
+++ b/CCU/EtOH/analyses/parameter_distributions/parameter-distributions_full.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IGB\Documents\GitHub\CCU\CCU\EtOH\analyses\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE27D1B4-56F3-4985-AD16-B9D3C1DED7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F69219-D17D-4E62-8FB5-6F944B9747B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="195">
   <si>
     <t>Parameter name</t>
   </si>
@@ -348,9 +348,6 @@
     <t>PowerUtility.price = x</t>
   </si>
   <si>
-    <t>makeup_MEA.price = x</t>
-  </si>
-  <si>
     <t>catalyst_MeOH.price = x</t>
   </si>
   <si>
@@ -423,9 +420,6 @@
     <t>cooling_tower_chemicals.price = x</t>
   </si>
   <si>
-    <t>natural_gas.price = x</t>
-  </si>
-  <si>
     <t>FGD_lime.price = x</t>
   </si>
   <si>
@@ -550,6 +544,84 @@
   </si>
   <si>
     <t>O2.price = x</t>
+  </si>
+  <si>
+    <t>R1102.GHSV = x</t>
+  </si>
+  <si>
+    <t>R1102.residence_time = x</t>
+  </si>
+  <si>
+    <t>R1102.reactions.X = x</t>
+  </si>
+  <si>
+    <t>U1102._default_equipment_lifetime['Full Process'] = x</t>
+  </si>
+  <si>
+    <t>R1103.WHSV = x</t>
+  </si>
+  <si>
+    <t>R1103.catalyst_density = x</t>
+  </si>
+  <si>
+    <t>R1103.catalyst_longevity = x</t>
+  </si>
+  <si>
+    <t>m3/hr/kg catalyst</t>
+  </si>
+  <si>
+    <t>catalyst_bireforming.price = x</t>
+  </si>
+  <si>
+    <t>Bi-reforming GHSV</t>
+  </si>
+  <si>
+    <t>Bi-reforming catalyst price</t>
+  </si>
+  <si>
+    <t>Bi-reforming catalyst longevity</t>
+  </si>
+  <si>
+    <t>Bi-reforming residence time</t>
+  </si>
+  <si>
+    <t>Bi-reforming conversion</t>
+  </si>
+  <si>
+    <t>https://pubs.acs.org/doi/10.1021/ja311796n</t>
+  </si>
+  <si>
+    <t>Methane membrane separator longevity</t>
+  </si>
+  <si>
+    <t>MeOH synthesis WHSV</t>
+  </si>
+  <si>
+    <t>R1103.porosity = x</t>
+  </si>
+  <si>
+    <t>MeOH synthesis catalyst density</t>
+  </si>
+  <si>
+    <t>MeOH synthesis catalyst longevity</t>
+  </si>
+  <si>
+    <t>MeOH synthesis porosity</t>
+  </si>
+  <si>
+    <t>MeOH synthesis catalyst price</t>
+  </si>
+  <si>
+    <t>natural_gas.price = natural_gas_2.price = x</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>makeup_MEA.price = makeup_MEA_2.price = x</t>
+  </si>
+  <si>
+    <t>B2</t>
   </si>
 </sst>
 </file>
@@ -595,7 +667,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -631,23 +703,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -664,7 +725,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -957,7 +1017,7 @@
     <col min="5" max="5" width="8.83984375" style="3" customWidth="1"/>
     <col min="6" max="6" width="14.47265625" style="5" customWidth="1"/>
     <col min="7" max="9" width="8.83984375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="38.26171875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="43.734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="22.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1188,7 +1248,7 @@
         <v>6.1074999999999997E-2</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1316,7 +1376,7 @@
         <v>0.10937626894095984</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1347,7 +1407,7 @@
         <v>0.1751604946094448</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1378,7 +1438,7 @@
         <v>1.0509629676566701</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1410,7 +1470,7 @@
         <v>0.49049082487137308</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1441,7 +1501,7 @@
         <v>0.11895995005808951</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1472,7 +1532,7 @@
         <v>1.4411192147993641</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1503,7 +1563,7 @@
         <v>1.0955492753754372</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1534,7 +1594,7 @@
         <v>1.1039239470817117</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1565,7 +1625,7 @@
         <v>2.5736459023251239</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1600,7 +1660,7 @@
         <v>0.16216800000000001</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1635,7 +1695,7 @@
         <v>4.2762225516771357</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1670,7 +1730,7 @@
         <v>1.3107390071921759E-3</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1706,7 +1766,7 @@
         <v>2.7185697926948881E-3</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1741,7 +1801,7 @@
         <v>-4.4395558211468962E-2</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1774,7 +1834,7 @@
         <v>0.25</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1807,7 +1867,7 @@
         <v>0.03</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1842,7 +1902,7 @@
         <v>0.11000000000000001</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1875,7 +1935,7 @@
         <v>0.94799999999999995</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1908,7 +1968,7 @@
         <v>0.97</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1941,7 +2001,7 @@
         <v>0.9</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -1974,7 +2034,7 @@
         <v>0.94799999999999995</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2007,7 +2067,7 @@
         <v>0.85</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2038,7 +2098,7 @@
         <v>0.88000000000000012</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2069,7 +2129,7 @@
         <v>0.93500000000000005</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2103,12 +2163,12 @@
         <v>0.13134000000000001</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>90</v>
@@ -2138,12 +2198,12 @@
         <v>0.34724082771509157</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>128</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>90</v>
@@ -2173,7 +2233,7 @@
         <v>0.42599999999999999</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -2196,7 +2256,7 @@
         <v>12</v>
       </c>
       <c r="G38" s="3">
-        <f t="shared" ref="G38:G51" si="3">E38*0.8</f>
+        <f t="shared" ref="G38:G53" si="3">E38*0.8</f>
         <v>1.1519999999999999</v>
       </c>
       <c r="I38" s="3">
@@ -2204,12 +2264,12 @@
         <v>1.728</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>103</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>91</v>
@@ -2221,550 +2281,546 @@
         <v>9</v>
       </c>
       <c r="E39" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0.312</v>
+      </c>
+      <c r="H39" s="3">
+        <f>E39</f>
+        <v>0.35</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J39" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="3">
+        <f>E40*0.8</f>
+        <v>0.46399999999999997</v>
+      </c>
+      <c r="H40" s="3">
+        <f>E40</f>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I40" s="3">
+        <f>E40*1.2</f>
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E41" s="3">
+        <f>H41</f>
+        <v>85</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="3">
+        <v>60</v>
+      </c>
+      <c r="H41" s="3">
+        <v>85</v>
+      </c>
+      <c r="I41" s="3">
+        <v>110</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="3">
+        <f>H42</f>
+        <v>12</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="3">
+        <v>10</v>
+      </c>
+      <c r="H42" s="3">
+        <v>12</v>
+      </c>
+      <c r="I42" s="3">
+        <v>15</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="3">
         <v>32.485780240073801</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F43" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G43" s="3">
         <f t="shared" si="3"/>
         <v>25.988624192059042</v>
       </c>
-      <c r="I39" s="3">
-        <f>1.2*E39</f>
+      <c r="I43" s="3">
+        <f>1.2*E43</f>
         <v>38.98293628808856</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="3" t="s">
+      <c r="J43" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" s="3" t="s">
+      <c r="B44" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E44" s="3">
         <v>0.6</v>
       </c>
-      <c r="F40" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G40" s="3">
-        <f t="shared" ref="G40:G45" si="4">E40*0.8</f>
+      <c r="F44" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="3">
+        <f t="shared" ref="G44:G49" si="4">E44*0.8</f>
         <v>0.48</v>
       </c>
-      <c r="H40" s="3">
-        <f t="shared" ref="H40:H47" si="5">E40</f>
+      <c r="H44" s="3">
+        <f t="shared" ref="H44:H49" si="5">E44</f>
         <v>0.6</v>
       </c>
-      <c r="I40" s="3">
-        <f t="shared" ref="I40:I45" si="6">E40*1.2</f>
+      <c r="I44" s="3">
+        <f t="shared" ref="I44:I49" si="6">E44*1.2</f>
         <v>0.72</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="3" t="s">
+      <c r="J44" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="B45" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E45" s="3">
         <v>0.21</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="F45" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="3">
         <f t="shared" si="4"/>
         <v>0.16800000000000001</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H45" s="3">
         <f t="shared" si="5"/>
         <v>0.21</v>
       </c>
-      <c r="I41" s="3">
+      <c r="I45" s="3">
         <f t="shared" si="6"/>
         <v>0.252</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="3" t="s">
+      <c r="J45" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" s="3" t="s">
+      <c r="B46" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E46" s="3">
         <v>2.8965517241379302</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="F46" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="3">
         <f t="shared" si="4"/>
         <v>2.3172413793103441</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H46" s="3">
         <f t="shared" si="5"/>
         <v>2.8965517241379302</v>
       </c>
-      <c r="I42" s="3">
+      <c r="I46" s="3">
         <f t="shared" si="6"/>
         <v>3.4758620689655162</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="3" t="s">
+      <c r="J46" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="B47" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E47" s="3">
         <v>1775</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="F47" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="3">
         <f t="shared" si="4"/>
         <v>1420</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H47" s="3">
         <f t="shared" si="5"/>
         <v>1775</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I47" s="3">
         <f t="shared" si="6"/>
         <v>2130</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="3" t="s">
+      <c r="J47" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="B48" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E48" s="3">
         <v>7884</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="F48" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" s="3">
         <f t="shared" si="4"/>
         <v>6307.2000000000007</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H48" s="3">
         <f t="shared" si="5"/>
         <v>7884</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I48" s="3">
         <f t="shared" si="6"/>
         <v>9460.7999999999993</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="3" t="s">
+      <c r="J48" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="B49" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E49" s="3">
         <v>0.5</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="F49" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="3">
         <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H49" s="3">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I49" s="3">
         <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G46" s="3">
-        <v>0.312</v>
-      </c>
-      <c r="H46" s="3">
-        <f t="shared" si="5"/>
-        <v>0.35</v>
-      </c>
-      <c r="I46" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="J46" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G47" s="3">
-        <f>E47*0.8</f>
-        <v>0.46399999999999997</v>
-      </c>
-      <c r="H47" s="3">
-        <f t="shared" si="5"/>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="I47" s="3">
-        <f>E47*1.2</f>
-        <v>0.69599999999999995</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="3" t="s">
+      <c r="J49" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B50" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" s="3" t="s">
+      <c r="C50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E50" s="3">
         <v>10</v>
       </c>
-      <c r="F48" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="F50" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="3">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="H48" s="3">
-        <f t="shared" ref="H48:H51" si="7">E48</f>
+      <c r="H50" s="3">
+        <f t="shared" ref="H50:H53" si="7">E50</f>
         <v>10</v>
       </c>
-      <c r="I48" s="3">
-        <f t="shared" ref="I48:I51" si="8">E48*1.2</f>
+      <c r="I50" s="3">
+        <f t="shared" ref="I50:I53" si="8">E50*1.2</f>
         <v>12</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="3" t="s">
+      <c r="J50" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B51" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="3" t="s">
+      <c r="C51" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E51" s="3">
         <v>1.01</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="F51" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="3">
         <f t="shared" si="3"/>
         <v>0.80800000000000005</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H51" s="3">
         <f t="shared" si="7"/>
         <v>1.01</v>
       </c>
-      <c r="I49" s="3">
+      <c r="I51" s="3">
         <f t="shared" si="8"/>
         <v>1.212</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="3" t="s">
+      <c r="J51" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B52" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="3" t="s">
+      <c r="C52" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E52" s="3">
         <v>1.38</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G50" s="3">
+      <c r="F52" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="3">
         <f t="shared" si="3"/>
         <v>1.1039999999999999</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H52" s="3">
         <f t="shared" si="7"/>
         <v>1.38</v>
       </c>
-      <c r="I50" s="3">
+      <c r="I52" s="3">
         <f t="shared" si="8"/>
         <v>1.6559999999999999</v>
       </c>
-      <c r="J50" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="3" t="s">
+      <c r="J52" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B53" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D51" s="3" t="s">
+      <c r="C53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E53" s="3">
         <v>1.05</v>
       </c>
-      <c r="F51" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G51" s="3">
+      <c r="F53" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" s="3">
         <f t="shared" si="3"/>
         <v>0.84000000000000008</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H53" s="3">
         <f t="shared" si="7"/>
         <v>1.05</v>
       </c>
-      <c r="I51" s="3">
+      <c r="I53" s="3">
         <f t="shared" si="8"/>
         <v>1.26</v>
       </c>
-      <c r="J51" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E52" s="3">
-        <f>H52</f>
-        <v>52.4</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G52" s="3">
-        <v>48</v>
-      </c>
-      <c r="H52" s="3">
-        <v>52.4</v>
-      </c>
-      <c r="I52" s="3">
-        <v>52.8</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G53" s="3">
-        <f>E53*0.8</f>
-        <v>0.18400000000000002</v>
-      </c>
-      <c r="H53" s="3">
-        <f>E53</f>
-        <v>0.23</v>
-      </c>
-      <c r="I53" s="3">
-        <f>E53*1.2</f>
-        <v>0.27600000000000002</v>
-      </c>
       <c r="J53" s="3" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="E54" s="3">
-        <v>0.1726</v>
+        <f>H54</f>
+        <v>52.4</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>18</v>
       </c>
       <c r="G54" s="3">
-        <f>E54*0.8</f>
-        <v>0.13808000000000001</v>
+        <v>48</v>
       </c>
       <c r="H54" s="3">
-        <f>E54</f>
-        <v>0.1726</v>
+        <v>52.4</v>
       </c>
       <c r="I54" s="3">
-        <f>E54*1.2</f>
-        <v>0.20712</v>
+        <v>52.8</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>169</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="3" t="s">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>15</v>
@@ -2773,34 +2829,33 @@
         <v>9</v>
       </c>
       <c r="E55" s="3">
-        <v>1.05</v>
+        <v>0.23</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>18</v>
       </c>
       <c r="G55" s="3">
-        <v>0.93</v>
+        <f>E55*0.8</f>
+        <v>0.18400000000000002</v>
       </c>
       <c r="H55" s="3">
         <f>E55</f>
-        <v>1.05</v>
+        <v>0.23</v>
       </c>
       <c r="I55" s="3">
-        <v>1.08</v>
+        <f>E55*1.2</f>
+        <v>0.27600000000000002</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K55" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="3" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>15</v>
@@ -2809,36 +2864,33 @@
         <v>81</v>
       </c>
       <c r="E56" s="3">
-        <v>11.05</v>
+        <v>0.1726</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>18</v>
       </c>
       <c r="G56" s="3">
         <f>E56*0.8</f>
-        <v>8.8400000000000016</v>
+        <v>0.13808000000000001</v>
       </c>
       <c r="H56" s="3">
-        <f t="shared" ref="H56:H58" si="9">E56</f>
-        <v>11.05</v>
+        <f>E56</f>
+        <v>0.1726</v>
       </c>
       <c r="I56" s="3">
-        <f>1.2*E56</f>
-        <v>13.26</v>
+        <f>E56*1.2</f>
+        <v>0.20712</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="K56" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>15</v>
@@ -2847,135 +2899,141 @@
         <v>9</v>
       </c>
       <c r="E57" s="3">
+        <v>1.05</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="H57" s="3">
+        <f>E57</f>
+        <v>1.05</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K57" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E58" s="3">
+        <v>11.05</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" s="3">
+        <f>E58*0.8</f>
+        <v>8.8400000000000016</v>
+      </c>
+      <c r="H58" s="3">
+        <f t="shared" ref="H58:H60" si="9">E58</f>
+        <v>11.05</v>
+      </c>
+      <c r="I58" s="3">
+        <f>1.2*E58</f>
+        <v>13.26</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="K58" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="3">
         <v>3.69</v>
       </c>
-      <c r="F57" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="F59" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" s="3">
         <v>3.13</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H59" s="3">
         <f t="shared" si="9"/>
         <v>3.69</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I59" s="3">
         <v>5.44</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="J59" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="3" t="s">
+      <c r="C60" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E60" s="3">
         <v>0.6</v>
       </c>
-      <c r="F58" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="F60" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" s="3">
         <v>0</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H60" s="3">
         <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I60" s="3">
         <v>1</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="K58" s="9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" s="3">
-        <v>8.4539160408078698E-2</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G59" s="3">
-        <v>7.8343341427146204E-2</v>
-      </c>
-      <c r="H59" s="3">
-        <f>E59</f>
-        <v>8.4539160408078698E-2</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0.110173994390799</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E60" s="3">
-        <v>0.435</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G60" s="3">
-        <f>E60*0.8</f>
-        <v>0.34800000000000003</v>
-      </c>
-      <c r="H60" s="3">
-        <f>E60</f>
-        <v>0.435</v>
-      </c>
-      <c r="I60" s="3">
-        <f>E60*1.2</f>
-        <v>0.52200000000000002</v>
-      </c>
       <c r="J60" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>15</v>
@@ -2984,20 +3042,20 @@
         <v>10</v>
       </c>
       <c r="E61" s="3">
-        <v>2.9000000000000001E-2</v>
+        <v>8.4539160408078698E-2</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>18</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>7.8343341427146204E-2</v>
       </c>
       <c r="H61" s="3">
         <f>E61</f>
-        <v>2.9000000000000001E-2</v>
+        <v>8.4539160408078698E-2</v>
       </c>
       <c r="I61" s="3">
-        <v>4.1000000000000002E-2</v>
+        <v>0.110173994390799</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>102</v>
@@ -3005,10 +3063,10 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>15</v>
@@ -3017,111 +3075,490 @@
         <v>89</v>
       </c>
       <c r="E62" s="3">
-        <v>1.9199999999999998E-2</v>
+        <v>0.435</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>18</v>
       </c>
       <c r="G62" s="3">
         <f>E62*0.8</f>
-        <v>1.5359999999999999E-2</v>
+        <v>0.34800000000000003</v>
       </c>
       <c r="H62" s="3">
-        <v>1.9199999999999998E-2</v>
+        <f>E62</f>
+        <v>0.435</v>
       </c>
       <c r="I62" s="3">
         <f>E62*1.2</f>
-        <v>2.3039999999999998E-2</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="3" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>164</v>
+        <v>10</v>
       </c>
       <c r="E63" s="3">
-        <f>H63</f>
-        <v>85</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>18</v>
       </c>
       <c r="G63" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H63" s="3">
-        <v>85</v>
+        <f>E63</f>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="I63" s="3">
-        <v>110</v>
-      </c>
-      <c r="J63" s="8" t="s">
-        <v>165</v>
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="3" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E64" s="3">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" s="3">
+        <f>E64*0.8</f>
+        <v>1.5359999999999999E-2</v>
+      </c>
+      <c r="H64" s="3">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="I64" s="3">
+        <f>E64*1.2</f>
+        <v>2.3039999999999998E-2</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E65" s="3">
+        <v>60</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" s="3">
+        <f>E65*0.8</f>
+        <v>48</v>
+      </c>
+      <c r="H65" s="3">
+        <f t="shared" ref="H65:H71" si="10">E65</f>
+        <v>60</v>
+      </c>
+      <c r="I65" s="3">
+        <f>E65*1.2</f>
+        <v>72</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="3">
+        <v>30</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" s="3">
+        <f>E66*0.8</f>
+        <v>24</v>
+      </c>
+      <c r="H66" s="3">
+        <f t="shared" si="10"/>
+        <v>30</v>
+      </c>
+      <c r="I66" s="3">
+        <f>E66*1.2</f>
+        <v>36</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E67" s="3">
+        <v>7884</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" s="3">
+        <f>E67*0.8</f>
+        <v>6307.2000000000007</v>
+      </c>
+      <c r="H67" s="3">
+        <f t="shared" si="10"/>
+        <v>7884</v>
+      </c>
+      <c r="I67" s="3">
+        <f>E67*1.2</f>
+        <v>9460.7999999999993</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E68" s="3">
+        <f>0.2/3600</f>
+        <v>5.5555555555555558E-5</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" s="3">
+        <f>E68*0.8</f>
+        <v>4.4444444444444447E-5</v>
+      </c>
+      <c r="H68" s="3">
+        <f t="shared" si="10"/>
+        <v>5.5555555555555558E-5</v>
+      </c>
+      <c r="I68" s="3">
+        <f>E68*1.2</f>
+        <v>6.666666666666667E-5</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="H69" s="3">
+        <f t="shared" si="10"/>
+        <v>0.75</v>
+      </c>
+      <c r="I69" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K69" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E64" s="3">
-        <f>H64</f>
-        <v>12</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G64" s="3">
-        <v>10</v>
-      </c>
-      <c r="H64" s="3">
-        <v>12</v>
-      </c>
-      <c r="I64" s="3">
-        <v>15</v>
-      </c>
-      <c r="J64" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="6"/>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="6"/>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="6"/>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="E70" s="3">
+        <v>7</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" s="3">
+        <v>5</v>
+      </c>
+      <c r="H70" s="3">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="I70" s="3">
+        <v>9</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="3">
+        <f>0.028 * 3600 / 34.8</f>
+        <v>2.896551724137931</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" s="3">
+        <f>E71*0.8</f>
+        <v>2.317241379310345</v>
+      </c>
+      <c r="H71" s="3">
+        <f t="shared" si="10"/>
+        <v>2.896551724137931</v>
+      </c>
+      <c r="I71" s="3">
+        <f>E71*1.2</f>
+        <v>3.4758620689655171</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" s="3">
+        <f t="shared" ref="G72:G74" si="11">E72*0.8</f>
+        <v>1600</v>
+      </c>
+      <c r="H72" s="3">
+        <f t="shared" ref="H72:H74" si="12">E72</f>
+        <v>2000</v>
+      </c>
+      <c r="I72" s="3">
+        <f t="shared" ref="I72:I74" si="13">E72*1.2</f>
+        <v>2400</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E73" s="3">
+        <v>7884</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" s="3">
+        <f t="shared" si="11"/>
+        <v>6307.2000000000007</v>
+      </c>
+      <c r="H73" s="3">
+        <f t="shared" si="12"/>
+        <v>7884</v>
+      </c>
+      <c r="I73" s="3">
+        <f t="shared" si="13"/>
+        <v>9460.7999999999993</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" s="3">
+        <f t="shared" si="11"/>
+        <v>0.4</v>
+      </c>
+      <c r="H74" s="3">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="I74" s="3">
+        <f t="shared" si="13"/>
+        <v>0.6</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="3">
+        <v>30</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" s="3">
+        <f>E75*0.8</f>
+        <v>24</v>
+      </c>
+      <c r="H75" s="3">
+        <f>E75</f>
+        <v>30</v>
+      </c>
+      <c r="I75" s="3">
+        <f>E75*1.2</f>
+        <v>36</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="6"/>
     </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="6"/>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="6"/>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="6"/>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.55000000000000004">
@@ -3130,7 +3567,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K58" r:id="rId1" xr:uid="{DD55F3D7-C741-4FAC-A1CE-89A46E4BB25C}"/>
+    <hyperlink ref="K60" r:id="rId1" xr:uid="{DD55F3D7-C741-4FAC-A1CE-89A46E4BB25C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
